--- a/employment_xlsx/PECH_MASTER_DOCUMENT_DASHBOARD.xlsx
+++ b/employment_xlsx/PECH_MASTER_DOCUMENT_DASHBOARD.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -70,6 +70,34 @@
       <i val="1"/>
       <color rgb="00999999"/>
       <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000099CC"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="00F5A623"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00888888"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00E8F4F8"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00AAAAAA"/>
+      <sz val="7"/>
     </font>
   </fonts>
   <fills count="9">
@@ -148,7 +176,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -191,6 +219,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -265,6 +308,36 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="628650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -554,8 +627,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:H88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -568,45 +642,31 @@
     <col width="26" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="6" customHeight="1">
-      <c r="A1" s="1" t="inlineStr"/>
-      <c r="B1" s="1" t="inlineStr"/>
-      <c r="C1" s="1" t="inlineStr"/>
-      <c r="D1" s="1" t="inlineStr"/>
-      <c r="E1" s="1" t="inlineStr"/>
-      <c r="F1" s="1" t="inlineStr"/>
-      <c r="G1" s="1" t="inlineStr"/>
-      <c r="H1" s="1" t="inlineStr"/>
-    </row>
-    <row r="2" ht="36" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="20" t="inlineStr">
         <is>
           <t>PECH GROUP HOLDINGS LTD</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>PECH MASTER DOCUMENT DASHBOARD</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-    </row>
-    <row r="4" ht="4" customHeight="1">
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>Technology &amp; Infrastructure Enablers for People</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="4" customHeight="1">
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="1" t="n"/>
+      <c r="C3" s="1" t="n"/>
+      <c r="D3" s="1" t="n"/>
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
+      <c r="H3" s="1" t="n"/>
+    </row>
+    <row r="4" ht="2" customHeight="1">
       <c r="A4" s="5" t="n"/>
       <c r="B4" s="5" t="n"/>
       <c r="C4" s="5" t="n"/>
@@ -616,238 +676,122 @@
       <c r="G4" s="5" t="n"/>
       <c r="H4" s="5" t="n"/>
     </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>Lagos, Nigeria  |  pechgroupholdings.tech  |  Confidential</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="8" customHeight="1"/>
+    <row r="7" ht="8" customHeight="1">
+      <c r="A7" s="1" t="inlineStr"/>
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr"/>
+      <c r="D7" s="1" t="inlineStr"/>
+      <c r="E7" s="1" t="inlineStr"/>
+      <c r="F7" s="1" t="inlineStr"/>
+      <c r="G7" s="1" t="inlineStr"/>
+      <c r="H7" s="1" t="inlineStr"/>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>PECH GROUP HOLDINGS LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>PECH MASTER DOCUMENT DASHBOARD</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>Lagos, Nigeria  |  pechgroupholdings.tech  |  All Employment + Business Documents  |  CONFIDENTIAL</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n"/>
-      <c r="H5" s="3" t="n"/>
-    </row>
-    <row r="6" ht="4" customHeight="1">
-      <c r="A6" s="5" t="n"/>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="1" t="n"/>
-      <c r="F6" s="1" t="n"/>
-      <c r="G6" s="1" t="n"/>
-      <c r="H6" s="1" t="n"/>
-    </row>
-    <row r="7" ht="8" customHeight="1"/>
-    <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="1" t="n"/>
+      <c r="F12" s="1" t="n"/>
+      <c r="G12" s="1" t="n"/>
+      <c r="H12" s="1" t="n"/>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  COMPLETE DOCUMENT INDEX (38 Excel Files)</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
-      <c r="E8" s="8" t="n"/>
-      <c r="F8" s="8" t="n"/>
-      <c r="G8" s="8" t="n"/>
-      <c r="H8" s="8" t="n"/>
-    </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>Document Name</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>Total Records</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="F15" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G15" s="9" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="H9" s="9" t="inlineStr">
+      <c r="H15" s="9" t="inlineStr">
         <is>
           <t>Google Sheets Link</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>Full-Time Employment Contract</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>Employment</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="n"/>
-      <c r="E10" s="10" t="n"/>
-      <c r="F10" s="10" t="n"/>
-      <c r="G10" s="10" t="n"/>
-      <c r="H10" s="11" t="inlineStr">
-        <is>
-          <t>(paste Google Sheets URL)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>Contract Worker Agreement</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>Employment</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="12" t="n"/>
-      <c r="G11" s="12" t="n"/>
-      <c r="H11" s="13" t="inlineStr">
-        <is>
-          <t>(paste Google Sheets URL)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>Internship Agreement</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>Employment</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="n"/>
-      <c r="E12" s="10" t="n"/>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="10" t="n"/>
-      <c r="H12" s="11" t="inlineStr">
-        <is>
-          <t>(paste Google Sheets URL)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>Office Marketer Agreement</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>Employment</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="12" t="n"/>
-      <c r="F13" s="12" t="n"/>
-      <c r="G13" s="12" t="n"/>
-      <c r="H13" s="13" t="inlineStr">
-        <is>
-          <t>(paste Google Sheets URL)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>Commission Marketer Agreement</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>Employment</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="n"/>
-      <c r="E14" s="10" t="n"/>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="10" t="n"/>
-      <c r="H14" s="11" t="inlineStr">
-        <is>
-          <t>(paste Google Sheets URL)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>Installer Agreement</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>Employment</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="12" t="n"/>
-      <c r="F15" s="12" t="n"/>
-      <c r="G15" s="12" t="n"/>
-      <c r="H15" s="13" t="inlineStr">
-        <is>
-          <t>(paste Google Sheets URL)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>API Developer Agreement</t>
+          <t>Full-Time Employment Contract</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
@@ -867,11 +811,11 @@
     </row>
     <row r="17">
       <c r="A17" s="12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Guarantor / Surety Form</t>
+          <t>Contract Worker Agreement</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -891,11 +835,11 @@
     </row>
     <row r="18">
       <c r="A18" s="10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Non-Disclosure Agreement</t>
+          <t>Internship Agreement</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
@@ -915,16 +859,16 @@
     </row>
     <row r="19">
       <c r="A19" s="12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Candidate Application Form</t>
+          <t>Office Marketer Agreement</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>HR Form</t>
+          <t>Employment</t>
         </is>
       </c>
       <c r="D19" s="12" t="n"/>
@@ -939,16 +883,16 @@
     </row>
     <row r="20">
       <c r="A20" s="10" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Interview Process &amp; Checklist</t>
+          <t>Commission Marketer Agreement</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>HR Form</t>
+          <t>Employment</t>
         </is>
       </c>
       <c r="D20" s="10" t="n"/>
@@ -963,16 +907,16 @@
     </row>
     <row r="21">
       <c r="A21" s="12" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Leave Request Form</t>
+          <t>Installer Agreement</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>HR Form</t>
+          <t>Employment</t>
         </is>
       </c>
       <c r="D21" s="12" t="n"/>
@@ -987,16 +931,16 @@
     </row>
     <row r="22">
       <c r="A22" s="10" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Staff ID Card Request</t>
+          <t>API Developer Agreement</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>HR Form</t>
+          <t>Employment</t>
         </is>
       </c>
       <c r="D22" s="10" t="n"/>
@@ -1011,16 +955,16 @@
     </row>
     <row r="23">
       <c r="A23" s="12" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Job Requirements Handbook</t>
+          <t>Guarantor / Surety Form</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>HR Reference</t>
+          <t>Employment</t>
         </is>
       </c>
       <c r="D23" s="12" t="n"/>
@@ -1035,16 +979,16 @@
     </row>
     <row r="24">
       <c r="A24" s="10" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Schedule B: KPI Templates</t>
+          <t>Non-Disclosure Agreement</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>HR Reference</t>
+          <t>Employment</t>
         </is>
       </c>
       <c r="D24" s="10" t="n"/>
@@ -1059,16 +1003,16 @@
     </row>
     <row r="25">
       <c r="A25" s="12" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Sales Invoice (Tax Invoice)</t>
+          <t>Candidate Application Form</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>HR Form</t>
         </is>
       </c>
       <c r="D25" s="12" t="n"/>
@@ -1083,16 +1027,16 @@
     </row>
     <row r="26">
       <c r="A26" s="10" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Proforma Invoice</t>
+          <t>Interview Process &amp; Checklist</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>HR Form</t>
         </is>
       </c>
       <c r="D26" s="10" t="n"/>
@@ -1107,16 +1051,16 @@
     </row>
     <row r="27">
       <c r="A27" s="12" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Quotation</t>
+          <t>Leave Request Form</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>HR Form</t>
         </is>
       </c>
       <c r="D27" s="12" t="n"/>
@@ -1131,16 +1075,16 @@
     </row>
     <row r="28">
       <c r="A28" s="10" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Purchase Order</t>
+          <t>Staff ID Card Request</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>HR Form</t>
         </is>
       </c>
       <c r="D28" s="10" t="n"/>
@@ -1155,16 +1099,16 @@
     </row>
     <row r="29">
       <c r="A29" s="12" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Credit Note</t>
+          <t>Job Requirements Handbook</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>HR Reference</t>
         </is>
       </c>
       <c r="D29" s="12" t="n"/>
@@ -1179,16 +1123,16 @@
     </row>
     <row r="30">
       <c r="A30" s="10" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Debit Note</t>
+          <t>Schedule B: KPI Templates</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>HR Reference</t>
         </is>
       </c>
       <c r="D30" s="10" t="n"/>
@@ -1203,11 +1147,11 @@
     </row>
     <row r="31">
       <c r="A31" s="12" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>Payment Voucher</t>
+          <t>Sales Invoice (Tax Invoice)</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
@@ -1227,11 +1171,11 @@
     </row>
     <row r="32">
       <c r="A32" s="10" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Payment Receipt</t>
+          <t>Proforma Invoice</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
@@ -1251,16 +1195,16 @@
     </row>
     <row r="33">
       <c r="A33" s="12" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>Expense Report</t>
+          <t>Quotation</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D33" s="12" t="n"/>
@@ -1275,16 +1219,16 @@
     </row>
     <row r="34">
       <c r="A34" s="10" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>Petty Cash Voucher</t>
+          <t>Purchase Order</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D34" s="10" t="n"/>
@@ -1299,16 +1243,16 @@
     </row>
     <row r="35">
       <c r="A35" s="12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>Delivery Note</t>
+          <t>Credit Note</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D35" s="12" t="n"/>
@@ -1323,16 +1267,16 @@
     </row>
     <row r="36">
       <c r="A36" s="10" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>Goods Received Note</t>
+          <t>Debit Note</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D36" s="10" t="n"/>
@@ -1347,16 +1291,16 @@
     </row>
     <row r="37">
       <c r="A37" s="12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>Stock Requisition Form</t>
+          <t>Payment Voucher</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D37" s="12" t="n"/>
@@ -1371,16 +1315,16 @@
     </row>
     <row r="38">
       <c r="A38" s="10" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>Waybill</t>
+          <t>Payment Receipt</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D38" s="10" t="n"/>
@@ -1395,11 +1339,11 @@
     </row>
     <row r="39">
       <c r="A39" s="12" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>Work Order</t>
+          <t>Expense Report</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
@@ -1419,11 +1363,11 @@
     </row>
     <row r="40">
       <c r="A40" s="10" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>Job Completion Report</t>
+          <t>Petty Cash Voucher</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
@@ -1443,16 +1387,16 @@
     </row>
     <row r="41">
       <c r="A41" s="12" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>Asset Register / Tracking Form</t>
+          <t>Delivery Note</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Assets</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D41" s="12" t="n"/>
@@ -1467,16 +1411,16 @@
     </row>
     <row r="42">
       <c r="A42" s="10" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>Visitor Log</t>
+          <t>Goods Received Note</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>Facilities</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D42" s="10" t="n"/>
@@ -1491,16 +1435,16 @@
     </row>
     <row r="43">
       <c r="A43" s="12" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>Incident Report Form</t>
+          <t>Stock Requisition Form</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D43" s="12" t="n"/>
@@ -1515,16 +1459,16 @@
     </row>
     <row r="44">
       <c r="A44" s="10" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>Media &amp; Public Communications</t>
+          <t>Waybill</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D44" s="10" t="n"/>
@@ -1539,16 +1483,16 @@
     </row>
     <row r="45">
       <c r="A45" s="12" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>Hackathon Rules &amp; Guidelines</t>
+          <t>Work Order</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Events</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D45" s="12" t="n"/>
@@ -1563,11 +1507,11 @@
     </row>
     <row r="46">
       <c r="A46" s="10" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>Installation Completion Certificate</t>
+          <t>Job Completion Report</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
@@ -1585,361 +1529,532 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="B47" s="12" t="inlineStr">
+        <is>
+          <t>Asset Register / Tracking Form</t>
+        </is>
+      </c>
+      <c r="C47" s="12" t="inlineStr">
+        <is>
+          <t>Assets</t>
+        </is>
+      </c>
+      <c r="D47" s="12" t="n"/>
+      <c r="E47" s="12" t="n"/>
+      <c r="F47" s="12" t="n"/>
+      <c r="G47" s="12" t="n"/>
+      <c r="H47" s="13" t="inlineStr">
+        <is>
+          <t>(paste Google Sheets URL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="n">
+        <v>33</v>
+      </c>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>Visitor Log</t>
+        </is>
+      </c>
+      <c r="C48" s="10" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="n"/>
+      <c r="E48" s="10" t="n"/>
+      <c r="F48" s="10" t="n"/>
+      <c r="G48" s="10" t="n"/>
+      <c r="H48" s="11" t="inlineStr">
+        <is>
+          <t>(paste Google Sheets URL)</t>
+        </is>
+      </c>
+    </row>
     <row r="49" ht="26" customHeight="1">
-      <c r="A49" s="7" t="inlineStr">
+      <c r="A49" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="B49" s="12" t="inlineStr">
+        <is>
+          <t>Incident Report Form</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="D49" s="12" t="n"/>
+      <c r="E49" s="12" t="n"/>
+      <c r="F49" s="12" t="n"/>
+      <c r="G49" s="12" t="n"/>
+      <c r="H49" s="13" t="inlineStr">
+        <is>
+          <t>(paste Google Sheets URL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="28" customHeight="1">
+      <c r="A50" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>Media &amp; Public Communications</t>
+        </is>
+      </c>
+      <c r="C50" s="10" t="inlineStr">
+        <is>
+          <t>Policy</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="n"/>
+      <c r="E50" s="10" t="n"/>
+      <c r="F50" s="10" t="n"/>
+      <c r="G50" s="10" t="n"/>
+      <c r="H50" s="11" t="inlineStr">
+        <is>
+          <t>(paste Google Sheets URL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>Hackathon Rules &amp; Guidelines</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+      <c r="D51" s="12" t="n"/>
+      <c r="E51" s="12" t="n"/>
+      <c r="F51" s="12" t="n"/>
+      <c r="G51" s="12" t="n"/>
+      <c r="H51" s="13" t="inlineStr">
+        <is>
+          <t>(paste Google Sheets URL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>Installation Completion Certificate</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="n"/>
+      <c r="E52" s="10" t="n"/>
+      <c r="F52" s="10" t="n"/>
+      <c r="G52" s="10" t="n"/>
+      <c r="H52" s="11" t="inlineStr">
+        <is>
+          <t>(paste Google Sheets URL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  DOCUMENT CATEGORIES SUMMARY</t>
         </is>
       </c>
-      <c r="B49" s="8" t="n"/>
-      <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="n"/>
-      <c r="E49" s="8" t="n"/>
-      <c r="F49" s="8" t="n"/>
-      <c r="G49" s="8" t="n"/>
-      <c r="H49" s="8" t="n"/>
-    </row>
-    <row r="50" ht="28" customHeight="1">
-      <c r="A50" s="9" t="inlineStr">
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B50" s="9" t="inlineStr">
+      <c r="B56" s="9" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C50" s="9" t="inlineStr">
+      <c r="C56" s="9" t="inlineStr">
         <is>
           <t>Document Count</t>
         </is>
       </c>
-      <c r="D50" s="9" t="inlineStr">
+      <c r="D56" s="9" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E50" s="9" t="inlineStr"/>
-      <c r="F50" s="9" t="inlineStr"/>
-      <c r="G50" s="9" t="inlineStr"/>
-      <c r="H50" s="9" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="14" t="n">
+      <c r="E56" s="9" t="inlineStr"/>
+      <c r="F56" s="9" t="inlineStr"/>
+      <c r="G56" s="9" t="inlineStr"/>
+      <c r="H56" s="9" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B51" s="14" t="inlineStr">
+      <c r="B57" s="14" t="inlineStr">
         <is>
           <t>Employment Contracts</t>
         </is>
       </c>
-      <c r="C51" s="14" t="inlineStr">
+      <c r="C57" s="14" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D51" s="14" t="inlineStr">
+      <c r="D57" s="14" t="inlineStr">
         <is>
           <t>All employment and contractor agreements</t>
         </is>
       </c>
-      <c r="E51" s="14" t="n"/>
-      <c r="F51" s="14" t="n"/>
-      <c r="G51" s="14" t="n"/>
-      <c r="H51" s="14" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="15" t="n">
+      <c r="E57" s="14" t="n"/>
+      <c r="F57" s="14" t="n"/>
+      <c r="G57" s="14" t="n"/>
+      <c r="H57" s="14" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="B52" s="15" t="inlineStr">
+      <c r="B58" s="15" t="inlineStr">
         <is>
           <t>HR Forms</t>
         </is>
       </c>
-      <c r="C52" s="15" t="inlineStr">
+      <c r="C58" s="15" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D52" s="15" t="inlineStr">
+      <c r="D58" s="15" t="inlineStr">
         <is>
           <t>Application, interview, leave, ID, handbook, KPIs</t>
         </is>
       </c>
-      <c r="E52" s="15" t="n"/>
-      <c r="F52" s="15" t="n"/>
-      <c r="G52" s="15" t="n"/>
-      <c r="H52" s="15" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="14" t="n">
+      <c r="E58" s="15" t="n"/>
+      <c r="F58" s="15" t="n"/>
+      <c r="G58" s="15" t="n"/>
+      <c r="H58" s="15" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="B53" s="14" t="inlineStr">
+      <c r="B59" s="14" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="C53" s="14" t="inlineStr">
+      <c r="C59" s="14" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D53" s="14" t="inlineStr">
+      <c r="D59" s="14" t="inlineStr">
         <is>
           <t>Invoices, POs, quotations, vouchers, receipts, notes</t>
         </is>
       </c>
-      <c r="E53" s="14" t="n"/>
-      <c r="F53" s="14" t="n"/>
-      <c r="G53" s="14" t="n"/>
-      <c r="H53" s="14" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="15" t="n">
+      <c r="E59" s="14" t="n"/>
+      <c r="F59" s="14" t="n"/>
+      <c r="G59" s="14" t="n"/>
+      <c r="H59" s="14" t="n"/>
+    </row>
+    <row r="60" ht="26" customHeight="1">
+      <c r="A60" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="B54" s="15" t="inlineStr">
+      <c r="B60" s="15" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="C54" s="15" t="inlineStr">
+      <c r="C60" s="15" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D54" s="15" t="inlineStr">
+      <c r="D60" s="15" t="inlineStr">
         <is>
           <t>Delivery, GRN, stock, waybill, work orders, jobs</t>
         </is>
       </c>
-      <c r="E54" s="15" t="n"/>
-      <c r="F54" s="15" t="n"/>
-      <c r="G54" s="15" t="n"/>
-      <c r="H54" s="15" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="14" t="n">
+      <c r="E60" s="15" t="n"/>
+      <c r="F60" s="15" t="n"/>
+      <c r="G60" s="15" t="n"/>
+      <c r="H60" s="15" t="n"/>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="B55" s="14" t="inlineStr">
+      <c r="B61" s="14" t="inlineStr">
         <is>
           <t>Assets / Facilities / Safety</t>
         </is>
       </c>
-      <c r="C55" s="14" t="inlineStr">
+      <c r="C61" s="14" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D55" s="14" t="inlineStr">
+      <c r="D61" s="14" t="inlineStr">
         <is>
           <t>Asset register, visitor log, incident reports</t>
         </is>
       </c>
-      <c r="E55" s="14" t="n"/>
-      <c r="F55" s="14" t="n"/>
-      <c r="G55" s="14" t="n"/>
-      <c r="H55" s="14" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="15" t="n">
+      <c r="E61" s="14" t="n"/>
+      <c r="F61" s="14" t="n"/>
+      <c r="G61" s="14" t="n"/>
+      <c r="H61" s="14" t="n"/>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="B56" s="15" t="inlineStr">
+      <c r="B62" s="15" t="inlineStr">
         <is>
           <t>Policy &amp; Events</t>
         </is>
       </c>
-      <c r="C56" s="15" t="inlineStr">
+      <c r="C62" s="15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D56" s="15" t="inlineStr">
+      <c r="D62" s="15" t="inlineStr">
         <is>
           <t>Media policy, hackathon tracker</t>
         </is>
       </c>
-      <c r="E56" s="15" t="n"/>
-      <c r="F56" s="15" t="n"/>
-      <c r="G56" s="15" t="n"/>
-      <c r="H56" s="15" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="16" t="n">
+      <c r="E62" s="15" t="n"/>
+      <c r="F62" s="15" t="n"/>
+      <c r="G62" s="15" t="n"/>
+      <c r="H62" s="15" t="n"/>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="16" t="n">
         <v>7</v>
       </c>
-      <c r="B57" s="16" t="inlineStr">
+      <c r="B63" s="16" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C57" s="16" t="inlineStr">
+      <c r="C63" s="16" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D57" s="16" t="inlineStr">
+      <c r="D63" s="16" t="inlineStr">
         <is>
           <t>Complete organizational document suite</t>
         </is>
       </c>
-      <c r="E57" s="16" t="n"/>
-      <c r="F57" s="16" t="n"/>
-      <c r="G57" s="16" t="n"/>
-      <c r="H57" s="16" t="n"/>
-    </row>
-    <row r="60" ht="26" customHeight="1">
-      <c r="A60" s="7" t="inlineStr">
+      <c r="E63" s="16" t="n"/>
+      <c r="F63" s="16" t="n"/>
+      <c r="G63" s="16" t="n"/>
+      <c r="H63" s="16" t="n"/>
+    </row>
+    <row r="64" ht="20" customHeight="1"/>
+    <row r="65" ht="20" customHeight="1"/>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  GOOGLE SHEETS SETUP INSTRUCTIONS</t>
-        </is>
-      </c>
-      <c r="B60" s="8" t="n"/>
-      <c r="C60" s="8" t="n"/>
-      <c r="D60" s="8" t="n"/>
-      <c r="E60" s="8" t="n"/>
-      <c r="F60" s="8" t="n"/>
-      <c r="G60" s="8" t="n"/>
-      <c r="H60" s="8" t="n"/>
-    </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1. Open Google Drive (drive.google.com)</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2. Click '+ New' &gt; 'File upload' &gt; Select one or more .xlsx files</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  3. Double-click the uploaded file to open in Google Sheets</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  4. Google Sheets will automatically convert the file</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  5. Click 'File' &gt; 'Save as Google Sheets' for native version</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  6. Share via 'Share' button with team members</t>
         </is>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  7. Set permissions: 'Editor' for relevant team, 'Viewer' for others</t>
+          <t xml:space="preserve">  1. Open Google Drive (drive.google.com)</t>
         </is>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  8. Copy the URL and paste in the 'Google Sheets Link' column above</t>
+          <t xml:space="preserve">  2. Click '+ New' &gt; 'File upload' &gt; Select one or more .xlsx files</t>
         </is>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  </t>
+          <t xml:space="preserve">  3. Double-click the uploaded file to open in Google Sheets</t>
         </is>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TIP: All dropdown validations, colors, and formatting are preserved!</t>
+          <t xml:space="preserve">  4. Google Sheets will automatically convert the file</t>
         </is>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TIP: Use 'File &gt; Make a copy' to create new templates from filled ones.</t>
+          <t xml:space="preserve">  5. Click 'File' &gt; 'Save as Google Sheets' for native version</t>
         </is>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="17" t="inlineStr">
         <is>
+          <t xml:space="preserve">  6. Share via 'Share' button with team members</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  7. Set permissions: 'Editor' for relevant team, 'Viewer' for others</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="3" customHeight="1">
+      <c r="A74" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  8. Copy the URL and paste in the 'Google Sheets Link' column above</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  </t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="3" customHeight="1">
+      <c r="A76" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  TIP: All dropdown validations, colors, and formatting are preserved!</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  TIP: Use 'File &gt; Make a copy' to create new templates from filled ones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="17" t="inlineStr">
+        <is>
           <t xml:space="preserve">  TIP: Upload all files to a shared 'PECH Documents' folder in Google Drive.</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="3" customHeight="1">
-      <c r="A74" s="5" t="n"/>
-      <c r="B74" s="5" t="n"/>
-      <c r="C74" s="5" t="n"/>
-      <c r="D74" s="5" t="n"/>
-      <c r="E74" s="5" t="n"/>
-      <c r="F74" s="5" t="n"/>
-      <c r="G74" s="5" t="n"/>
-      <c r="H74" s="5" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="18" t="inlineStr">
+    <row r="79"/>
+    <row r="80">
+      <c r="A80" s="5" t="n"/>
+      <c r="B80" s="5" t="n"/>
+      <c r="C80" s="5" t="n"/>
+      <c r="D80" s="5" t="n"/>
+      <c r="E80" s="5" t="n"/>
+      <c r="F80" s="5" t="n"/>
+      <c r="G80" s="5" t="n"/>
+      <c r="H80" s="5" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="18" t="inlineStr">
         <is>
           <t>PECH Group Holdings Ltd  |  Confidential  |  pechgroupholdings.tech  |  Technology &amp; Infrastructure Enablers for People</t>
         </is>
       </c>
-      <c r="B75" s="19" t="n"/>
-      <c r="C75" s="19" t="n"/>
-      <c r="D75" s="19" t="n"/>
-      <c r="E75" s="19" t="n"/>
-      <c r="F75" s="19" t="n"/>
-      <c r="G75" s="19" t="n"/>
-      <c r="H75" s="19" t="n"/>
-    </row>
-    <row r="76" ht="3" customHeight="1">
-      <c r="A76" s="1" t="n"/>
-      <c r="B76" s="1" t="n"/>
-      <c r="C76" s="1" t="n"/>
-      <c r="D76" s="1" t="n"/>
-      <c r="E76" s="1" t="n"/>
-      <c r="F76" s="1" t="n"/>
-      <c r="G76" s="1" t="n"/>
-      <c r="H76" s="1" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n"/>
+      <c r="B82" s="1" t="n"/>
+      <c r="C82" s="1" t="n"/>
+      <c r="D82" s="1" t="n"/>
+      <c r="E82" s="1" t="n"/>
+      <c r="F82" s="1" t="n"/>
+      <c r="G82" s="1" t="n"/>
+      <c r="H82" s="1" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="23" t="inlineStr">
+        <is>
+          <t>PECH GROUP HOLDINGS LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="23" t="inlineStr">
+        <is>
+          <t>PECH GROUP HOLDINGS LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="23" t="inlineStr">
+        <is>
+          <t>PECH GROUP HOLDINGS LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="24" t="inlineStr">
+        <is>
+          <t>Confidential — PECH Group Holdings Ltd — Lagos, Nigeria — pechgroupholdings.tech</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n"/>
+      <c r="B88" s="1" t="n"/>
+      <c r="C88" s="1" t="n"/>
+      <c r="D88" s="1" t="n"/>
+      <c r="E88" s="1" t="n"/>
+      <c r="F88" s="1" t="n"/>
+      <c r="G88" s="1" t="n"/>
+      <c r="H88" s="1" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="24">
     <mergeCell ref="A67:H67"/>
     <mergeCell ref="A64:H64"/>
     <mergeCell ref="A60:H60"/>
     <mergeCell ref="A49:H49"/>
+    <mergeCell ref="A1:H1"/>
     <mergeCell ref="A61:H61"/>
     <mergeCell ref="A70:H70"/>
     <mergeCell ref="A69:H69"/>
+    <mergeCell ref="A87:H87"/>
     <mergeCell ref="A65:H65"/>
     <mergeCell ref="A66:H66"/>
     <mergeCell ref="A75:H75"/>
+    <mergeCell ref="A84:H84"/>
     <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A86:H86"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A71:H71"/>
+    <mergeCell ref="A85:H85"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="A8:H8"/>
     <mergeCell ref="A62:H62"/>
@@ -1949,5 +2064,14 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;8 PECH Group Holdings Ltd | Confidential</oddHeader>
+    <oddFooter>&amp;C&amp;7 PECH Group Holdings Ltd | Lagos, Nigeria | pechgroupholdings.tech</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/employment_xlsx/PECH_MASTER_DOCUMENT_DASHBOARD.xlsx
+++ b/employment_xlsx/PECH_MASTER_DOCUMENT_DASHBOARD.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -70,34 +70,6 @@
       <i val="1"/>
       <color rgb="00999999"/>
       <sz val="8"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="000099CC"/>
-      <sz val="18"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <i val="1"/>
-      <color rgb="00F5A623"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <color rgb="00888888"/>
-      <sz val="7"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="00E8F4F8"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <color rgb="00AAAAAA"/>
-      <sz val="7"/>
     </font>
   </fonts>
   <fills count="9">
@@ -176,7 +148,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -219,21 +191,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -308,36 +265,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1905000" cy="628650"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -629,7 +556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H88"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -642,31 +569,45 @@
     <col width="26" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="20" t="inlineStr">
+    <row r="1" ht="6" customHeight="1">
+      <c r="A1" s="1" t="inlineStr"/>
+      <c r="B1" s="1" t="inlineStr"/>
+      <c r="C1" s="1" t="inlineStr"/>
+      <c r="D1" s="1" t="inlineStr"/>
+      <c r="E1" s="1" t="inlineStr"/>
+      <c r="F1" s="1" t="inlineStr"/>
+      <c r="G1" s="1" t="inlineStr"/>
+      <c r="H1" s="1" t="inlineStr"/>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>PECH GROUP HOLDINGS LTD</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="21" t="inlineStr">
-        <is>
-          <t>Technology &amp; Infrastructure Enablers for People</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="4" customHeight="1">
-      <c r="A3" s="1" t="n"/>
-      <c r="B3" s="1" t="n"/>
-      <c r="C3" s="1" t="n"/>
-      <c r="D3" s="1" t="n"/>
-      <c r="E3" s="1" t="n"/>
-      <c r="F3" s="1" t="n"/>
-      <c r="G3" s="1" t="n"/>
-      <c r="H3" s="1" t="n"/>
-    </row>
-    <row r="4" ht="2" customHeight="1">
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>PECH MASTER DOCUMENT DASHBOARD</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="4" customHeight="1">
       <c r="A4" s="5" t="n"/>
       <c r="B4" s="5" t="n"/>
       <c r="C4" s="5" t="n"/>
@@ -676,122 +617,238 @@
       <c r="G4" s="5" t="n"/>
       <c r="H4" s="5" t="n"/>
     </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="22" t="inlineStr">
-        <is>
-          <t>Lagos, Nigeria  |  pechgroupholdings.tech  |  Confidential</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="8" customHeight="1"/>
-    <row r="7" ht="8" customHeight="1">
-      <c r="A7" s="1" t="inlineStr"/>
-      <c r="B7" s="1" t="inlineStr"/>
-      <c r="C7" s="1" t="inlineStr"/>
-      <c r="D7" s="1" t="inlineStr"/>
-      <c r="E7" s="1" t="inlineStr"/>
-      <c r="F7" s="1" t="inlineStr"/>
-      <c r="G7" s="1" t="inlineStr"/>
-      <c r="H7" s="1" t="inlineStr"/>
-    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Lagos, Nigeria  |  pechgroupholdings.tech  |  All Employment + Business Documents  |  CONFIDENTIAL</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6" ht="4" customHeight="1">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="1" t="n"/>
+      <c r="F6" s="1" t="n"/>
+      <c r="G6" s="1" t="n"/>
+      <c r="H6" s="1" t="n"/>
+    </row>
+    <row r="7" ht="8" customHeight="1"/>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>PECH GROUP HOLDINGS LTD</t>
-        </is>
-      </c>
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  COMPLETE DOCUMENT INDEX (38 Excel Files)</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
+      <c r="H8" s="8" t="n"/>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>PECH MASTER DOCUMENT DASHBOARD</t>
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Document Name</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Total Records</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>Google Sheets Link</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
+      <c r="A10" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Full-Time Employment Contract</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="10" t="n"/>
+      <c r="F10" s="10" t="n"/>
+      <c r="G10" s="10" t="n"/>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>(paste Google Sheets URL)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Lagos, Nigeria  |  pechgroupholdings.tech  |  All Employment + Business Documents  |  CONFIDENTIAL</t>
+      <c r="A11" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Contract Worker Agreement</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="n"/>
+      <c r="E11" s="12" t="n"/>
+      <c r="F11" s="12" t="n"/>
+      <c r="G11" s="12" t="n"/>
+      <c r="H11" s="13" t="inlineStr">
+        <is>
+          <t>(paste Google Sheets URL)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="1" t="n"/>
-      <c r="F12" s="1" t="n"/>
-      <c r="G12" s="1" t="n"/>
-      <c r="H12" s="1" t="n"/>
-    </row>
-    <row r="13"/>
+      <c r="A12" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Internship Agreement</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
+      <c r="G12" s="10" t="n"/>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>(paste Google Sheets URL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Office Marketer Agreement</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="n"/>
+      <c r="E13" s="12" t="n"/>
+      <c r="F13" s="12" t="n"/>
+      <c r="G13" s="12" t="n"/>
+      <c r="H13" s="13" t="inlineStr">
+        <is>
+          <t>(paste Google Sheets URL)</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  COMPLETE DOCUMENT INDEX (38 Excel Files)</t>
+      <c r="A14" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Commission Marketer Agreement</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
+      <c r="G14" s="10" t="n"/>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>(paste Google Sheets URL)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Document Name</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>Total Records</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="H15" s="9" t="inlineStr">
-        <is>
-          <t>Google Sheets Link</t>
+      <c r="A15" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Installer Agreement</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n"/>
+      <c r="E15" s="12" t="n"/>
+      <c r="F15" s="12" t="n"/>
+      <c r="G15" s="12" t="n"/>
+      <c r="H15" s="13" t="inlineStr">
+        <is>
+          <t>(paste Google Sheets URL)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Full-Time Employment Contract</t>
+          <t>API Developer Agreement</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
@@ -811,11 +868,11 @@
     </row>
     <row r="17">
       <c r="A17" s="12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Contract Worker Agreement</t>
+          <t>Guarantor / Surety Form</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -835,11 +892,11 @@
     </row>
     <row r="18">
       <c r="A18" s="10" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Internship Agreement</t>
+          <t>Non-Disclosure Agreement</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
@@ -859,16 +916,16 @@
     </row>
     <row r="19">
       <c r="A19" s="12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Office Marketer Agreement</t>
+          <t>Candidate Application Form</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Employment</t>
+          <t>HR Form</t>
         </is>
       </c>
       <c r="D19" s="12" t="n"/>
@@ -883,16 +940,16 @@
     </row>
     <row r="20">
       <c r="A20" s="10" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Commission Marketer Agreement</t>
+          <t>Interview Process &amp; Checklist</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>Employment</t>
+          <t>HR Form</t>
         </is>
       </c>
       <c r="D20" s="10" t="n"/>
@@ -907,16 +964,16 @@
     </row>
     <row r="21">
       <c r="A21" s="12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Installer Agreement</t>
+          <t>Leave Request Form</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Employment</t>
+          <t>HR Form</t>
         </is>
       </c>
       <c r="D21" s="12" t="n"/>
@@ -931,16 +988,16 @@
     </row>
     <row r="22">
       <c r="A22" s="10" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>API Developer Agreement</t>
+          <t>Staff ID Card Request</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>Employment</t>
+          <t>HR Form</t>
         </is>
       </c>
       <c r="D22" s="10" t="n"/>
@@ -955,16 +1012,16 @@
     </row>
     <row r="23">
       <c r="A23" s="12" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Guarantor / Surety Form</t>
+          <t>Job Requirements Handbook</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Employment</t>
+          <t>HR Reference</t>
         </is>
       </c>
       <c r="D23" s="12" t="n"/>
@@ -979,16 +1036,16 @@
     </row>
     <row r="24">
       <c r="A24" s="10" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Non-Disclosure Agreement</t>
+          <t>Schedule B: KPI Templates</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>Employment</t>
+          <t>HR Reference</t>
         </is>
       </c>
       <c r="D24" s="10" t="n"/>
@@ -1003,16 +1060,16 @@
     </row>
     <row r="25">
       <c r="A25" s="12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Candidate Application Form</t>
+          <t>Sales Invoice (Tax Invoice)</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>HR Form</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D25" s="12" t="n"/>
@@ -1027,16 +1084,16 @@
     </row>
     <row r="26">
       <c r="A26" s="10" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Interview Process &amp; Checklist</t>
+          <t>Proforma Invoice</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>HR Form</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D26" s="10" t="n"/>
@@ -1051,16 +1108,16 @@
     </row>
     <row r="27">
       <c r="A27" s="12" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Leave Request Form</t>
+          <t>Quotation</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>HR Form</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D27" s="12" t="n"/>
@@ -1075,16 +1132,16 @@
     </row>
     <row r="28">
       <c r="A28" s="10" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Staff ID Card Request</t>
+          <t>Purchase Order</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>HR Form</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D28" s="10" t="n"/>
@@ -1099,16 +1156,16 @@
     </row>
     <row r="29">
       <c r="A29" s="12" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Job Requirements Handbook</t>
+          <t>Credit Note</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>HR Reference</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D29" s="12" t="n"/>
@@ -1123,16 +1180,16 @@
     </row>
     <row r="30">
       <c r="A30" s="10" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Schedule B: KPI Templates</t>
+          <t>Debit Note</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>HR Reference</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D30" s="10" t="n"/>
@@ -1147,11 +1204,11 @@
     </row>
     <row r="31">
       <c r="A31" s="12" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>Sales Invoice (Tax Invoice)</t>
+          <t>Payment Voucher</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
@@ -1171,11 +1228,11 @@
     </row>
     <row r="32">
       <c r="A32" s="10" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Proforma Invoice</t>
+          <t>Payment Receipt</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
@@ -1195,16 +1252,16 @@
     </row>
     <row r="33">
       <c r="A33" s="12" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>Quotation</t>
+          <t>Expense Report</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D33" s="12" t="n"/>
@@ -1219,16 +1276,16 @@
     </row>
     <row r="34">
       <c r="A34" s="10" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>Purchase Order</t>
+          <t>Petty Cash Voucher</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D34" s="10" t="n"/>
@@ -1243,16 +1300,16 @@
     </row>
     <row r="35">
       <c r="A35" s="12" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>Credit Note</t>
+          <t>Delivery Note</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D35" s="12" t="n"/>
@@ -1267,16 +1324,16 @@
     </row>
     <row r="36">
       <c r="A36" s="10" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>Debit Note</t>
+          <t>Goods Received Note</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D36" s="10" t="n"/>
@@ -1291,16 +1348,16 @@
     </row>
     <row r="37">
       <c r="A37" s="12" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>Payment Voucher</t>
+          <t>Stock Requisition Form</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D37" s="12" t="n"/>
@@ -1315,16 +1372,16 @@
     </row>
     <row r="38">
       <c r="A38" s="10" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>Payment Receipt</t>
+          <t>Waybill</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D38" s="10" t="n"/>
@@ -1339,11 +1396,11 @@
     </row>
     <row r="39">
       <c r="A39" s="12" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>Expense Report</t>
+          <t>Work Order</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
@@ -1363,11 +1420,11 @@
     </row>
     <row r="40">
       <c r="A40" s="10" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>Petty Cash Voucher</t>
+          <t>Job Completion Report</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
@@ -1387,16 +1444,16 @@
     </row>
     <row r="41">
       <c r="A41" s="12" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>Delivery Note</t>
+          <t>Asset Register / Tracking Form</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Assets</t>
         </is>
       </c>
       <c r="D41" s="12" t="n"/>
@@ -1411,16 +1468,16 @@
     </row>
     <row r="42">
       <c r="A42" s="10" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>Goods Received Note</t>
+          <t>Visitor Log</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Facilities</t>
         </is>
       </c>
       <c r="D42" s="10" t="n"/>
@@ -1435,16 +1492,16 @@
     </row>
     <row r="43">
       <c r="A43" s="12" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>Stock Requisition Form</t>
+          <t>Incident Report Form</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="D43" s="12" t="n"/>
@@ -1459,16 +1516,16 @@
     </row>
     <row r="44">
       <c r="A44" s="10" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>Waybill</t>
+          <t>Media &amp; Public Communications</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="D44" s="10" t="n"/>
@@ -1483,16 +1540,16 @@
     </row>
     <row r="45">
       <c r="A45" s="12" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>Work Order</t>
+          <t>Hackathon Rules &amp; Guidelines</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Events</t>
         </is>
       </c>
       <c r="D45" s="12" t="n"/>
@@ -1507,11 +1564,11 @@
     </row>
     <row r="46">
       <c r="A46" s="10" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>Job Completion Report</t>
+          <t>Installation Completion Certificate</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
@@ -1529,532 +1586,361 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="B47" s="12" t="inlineStr">
-        <is>
-          <t>Asset Register / Tracking Form</t>
-        </is>
-      </c>
-      <c r="C47" s="12" t="inlineStr">
-        <is>
-          <t>Assets</t>
-        </is>
-      </c>
-      <c r="D47" s="12" t="n"/>
-      <c r="E47" s="12" t="n"/>
-      <c r="F47" s="12" t="n"/>
-      <c r="G47" s="12" t="n"/>
-      <c r="H47" s="13" t="inlineStr">
-        <is>
-          <t>(paste Google Sheets URL)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="10" t="n">
-        <v>33</v>
-      </c>
-      <c r="B48" s="10" t="inlineStr">
-        <is>
-          <t>Visitor Log</t>
-        </is>
-      </c>
-      <c r="C48" s="10" t="inlineStr">
-        <is>
-          <t>Facilities</t>
-        </is>
-      </c>
-      <c r="D48" s="10" t="n"/>
-      <c r="E48" s="10" t="n"/>
-      <c r="F48" s="10" t="n"/>
-      <c r="G48" s="10" t="n"/>
-      <c r="H48" s="11" t="inlineStr">
-        <is>
-          <t>(paste Google Sheets URL)</t>
-        </is>
-      </c>
-    </row>
     <row r="49" ht="26" customHeight="1">
-      <c r="A49" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="B49" s="12" t="inlineStr">
-        <is>
-          <t>Incident Report Form</t>
-        </is>
-      </c>
-      <c r="C49" s="12" t="inlineStr">
-        <is>
-          <t>Safety</t>
-        </is>
-      </c>
-      <c r="D49" s="12" t="n"/>
-      <c r="E49" s="12" t="n"/>
-      <c r="F49" s="12" t="n"/>
-      <c r="G49" s="12" t="n"/>
-      <c r="H49" s="13" t="inlineStr">
-        <is>
-          <t>(paste Google Sheets URL)</t>
-        </is>
-      </c>
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  DOCUMENT CATEGORIES SUMMARY</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="n"/>
+      <c r="C49" s="8" t="n"/>
+      <c r="D49" s="8" t="n"/>
+      <c r="E49" s="8" t="n"/>
+      <c r="F49" s="8" t="n"/>
+      <c r="G49" s="8" t="n"/>
+      <c r="H49" s="8" t="n"/>
     </row>
     <row r="50" ht="28" customHeight="1">
-      <c r="A50" s="10" t="n">
-        <v>35</v>
-      </c>
-      <c r="B50" s="10" t="inlineStr">
-        <is>
-          <t>Media &amp; Public Communications</t>
-        </is>
-      </c>
-      <c r="C50" s="10" t="inlineStr">
-        <is>
-          <t>Policy</t>
-        </is>
-      </c>
-      <c r="D50" s="10" t="n"/>
-      <c r="E50" s="10" t="n"/>
-      <c r="F50" s="10" t="n"/>
-      <c r="G50" s="10" t="n"/>
-      <c r="H50" s="11" t="inlineStr">
-        <is>
-          <t>(paste Google Sheets URL)</t>
-        </is>
-      </c>
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>Document Count</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="inlineStr"/>
+      <c r="F50" s="9" t="inlineStr"/>
+      <c r="G50" s="9" t="inlineStr"/>
+      <c r="H50" s="9" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="12" t="n">
-        <v>36</v>
-      </c>
-      <c r="B51" s="12" t="inlineStr">
-        <is>
-          <t>Hackathon Rules &amp; Guidelines</t>
-        </is>
-      </c>
-      <c r="C51" s="12" t="inlineStr">
-        <is>
-          <t>Events</t>
-        </is>
-      </c>
-      <c r="D51" s="12" t="n"/>
-      <c r="E51" s="12" t="n"/>
-      <c r="F51" s="12" t="n"/>
-      <c r="G51" s="12" t="n"/>
-      <c r="H51" s="13" t="inlineStr">
-        <is>
-          <t>(paste Google Sheets URL)</t>
-        </is>
-      </c>
+      <c r="A51" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>Employment Contracts</t>
+        </is>
+      </c>
+      <c r="C51" s="14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D51" s="14" t="inlineStr">
+        <is>
+          <t>All employment and contractor agreements</t>
+        </is>
+      </c>
+      <c r="E51" s="14" t="n"/>
+      <c r="F51" s="14" t="n"/>
+      <c r="G51" s="14" t="n"/>
+      <c r="H51" s="14" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="10" t="n">
-        <v>37</v>
-      </c>
-      <c r="B52" s="10" t="inlineStr">
-        <is>
-          <t>Installation Completion Certificate</t>
-        </is>
-      </c>
-      <c r="C52" s="10" t="inlineStr">
+      <c r="A52" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="B52" s="15" t="inlineStr">
+        <is>
+          <t>HR Forms</t>
+        </is>
+      </c>
+      <c r="C52" s="15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D52" s="15" t="inlineStr">
+        <is>
+          <t>Application, interview, leave, ID, handbook, KPIs</t>
+        </is>
+      </c>
+      <c r="E52" s="15" t="n"/>
+      <c r="F52" s="15" t="n"/>
+      <c r="G52" s="15" t="n"/>
+      <c r="H52" s="15" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B53" s="14" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C53" s="14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D53" s="14" t="inlineStr">
+        <is>
+          <t>Invoices, POs, quotations, vouchers, receipts, notes</t>
+        </is>
+      </c>
+      <c r="E53" s="14" t="n"/>
+      <c r="F53" s="14" t="n"/>
+      <c r="G53" s="14" t="n"/>
+      <c r="H53" s="14" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="B54" s="15" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="D52" s="10" t="n"/>
-      <c r="E52" s="10" t="n"/>
-      <c r="F52" s="10" t="n"/>
-      <c r="G52" s="10" t="n"/>
-      <c r="H52" s="11" t="inlineStr">
-        <is>
-          <t>(paste Google Sheets URL)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53"/>
-    <row r="54"/>
+      <c r="C54" s="15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D54" s="15" t="inlineStr">
+        <is>
+          <t>Delivery, GRN, stock, waybill, work orders, jobs</t>
+        </is>
+      </c>
+      <c r="E54" s="15" t="n"/>
+      <c r="F54" s="15" t="n"/>
+      <c r="G54" s="15" t="n"/>
+      <c r="H54" s="15" t="n"/>
+    </row>
     <row r="55">
-      <c r="A55" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  DOCUMENT CATEGORIES SUMMARY</t>
-        </is>
-      </c>
+      <c r="A55" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t>Assets / Facilities / Safety</t>
+        </is>
+      </c>
+      <c r="C55" s="14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D55" s="14" t="inlineStr">
+        <is>
+          <t>Asset register, visitor log, incident reports</t>
+        </is>
+      </c>
+      <c r="E55" s="14" t="n"/>
+      <c r="F55" s="14" t="n"/>
+      <c r="G55" s="14" t="n"/>
+      <c r="H55" s="14" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="9" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B56" s="9" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="C56" s="9" t="inlineStr">
-        <is>
-          <t>Document Count</t>
-        </is>
-      </c>
-      <c r="D56" s="9" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="E56" s="9" t="inlineStr"/>
-      <c r="F56" s="9" t="inlineStr"/>
-      <c r="G56" s="9" t="inlineStr"/>
-      <c r="H56" s="9" t="inlineStr"/>
+      <c r="A56" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B56" s="15" t="inlineStr">
+        <is>
+          <t>Policy &amp; Events</t>
+        </is>
+      </c>
+      <c r="C56" s="15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D56" s="15" t="inlineStr">
+        <is>
+          <t>Media policy, hackathon tracker</t>
+        </is>
+      </c>
+      <c r="E56" s="15" t="n"/>
+      <c r="F56" s="15" t="n"/>
+      <c r="G56" s="15" t="n"/>
+      <c r="H56" s="15" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="B57" s="14" t="inlineStr">
-        <is>
-          <t>Employment Contracts</t>
-        </is>
-      </c>
-      <c r="C57" s="14" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D57" s="14" t="inlineStr">
-        <is>
-          <t>All employment and contractor agreements</t>
-        </is>
-      </c>
-      <c r="E57" s="14" t="n"/>
-      <c r="F57" s="14" t="n"/>
-      <c r="G57" s="14" t="n"/>
-      <c r="H57" s="14" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="B58" s="15" t="inlineStr">
-        <is>
-          <t>HR Forms</t>
-        </is>
-      </c>
-      <c r="C58" s="15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D58" s="15" t="inlineStr">
-        <is>
-          <t>Application, interview, leave, ID, handbook, KPIs</t>
-        </is>
-      </c>
-      <c r="E58" s="15" t="n"/>
-      <c r="F58" s="15" t="n"/>
-      <c r="G58" s="15" t="n"/>
-      <c r="H58" s="15" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="B59" s="14" t="inlineStr">
-        <is>
-          <t>Finance</t>
-        </is>
-      </c>
-      <c r="C59" s="14" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D59" s="14" t="inlineStr">
-        <is>
-          <t>Invoices, POs, quotations, vouchers, receipts, notes</t>
-        </is>
-      </c>
-      <c r="E59" s="14" t="n"/>
-      <c r="F59" s="14" t="n"/>
-      <c r="G59" s="14" t="n"/>
-      <c r="H59" s="14" t="n"/>
+      <c r="A57" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="B57" s="16" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C57" s="16" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D57" s="16" t="inlineStr">
+        <is>
+          <t>Complete organizational document suite</t>
+        </is>
+      </c>
+      <c r="E57" s="16" t="n"/>
+      <c r="F57" s="16" t="n"/>
+      <c r="G57" s="16" t="n"/>
+      <c r="H57" s="16" t="n"/>
     </row>
     <row r="60" ht="26" customHeight="1">
-      <c r="A60" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="B60" s="15" t="inlineStr">
-        <is>
-          <t>Operations</t>
-        </is>
-      </c>
-      <c r="C60" s="15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D60" s="15" t="inlineStr">
-        <is>
-          <t>Delivery, GRN, stock, waybill, work orders, jobs</t>
-        </is>
-      </c>
-      <c r="E60" s="15" t="n"/>
-      <c r="F60" s="15" t="n"/>
-      <c r="G60" s="15" t="n"/>
-      <c r="H60" s="15" t="n"/>
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  GOOGLE SHEETS SETUP INSTRUCTIONS</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="n"/>
+      <c r="C60" s="8" t="n"/>
+      <c r="D60" s="8" t="n"/>
+      <c r="E60" s="8" t="n"/>
+      <c r="F60" s="8" t="n"/>
+      <c r="G60" s="8" t="n"/>
+      <c r="H60" s="8" t="n"/>
     </row>
     <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="B61" s="14" t="inlineStr">
-        <is>
-          <t>Assets / Facilities / Safety</t>
-        </is>
-      </c>
-      <c r="C61" s="14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D61" s="14" t="inlineStr">
-        <is>
-          <t>Asset register, visitor log, incident reports</t>
-        </is>
-      </c>
-      <c r="E61" s="14" t="n"/>
-      <c r="F61" s="14" t="n"/>
-      <c r="G61" s="14" t="n"/>
-      <c r="H61" s="14" t="n"/>
+      <c r="A61" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1. Open Google Drive (drive.google.com)</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="B62" s="15" t="inlineStr">
-        <is>
-          <t>Policy &amp; Events</t>
-        </is>
-      </c>
-      <c r="C62" s="15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D62" s="15" t="inlineStr">
-        <is>
-          <t>Media policy, hackathon tracker</t>
-        </is>
-      </c>
-      <c r="E62" s="15" t="n"/>
-      <c r="F62" s="15" t="n"/>
-      <c r="G62" s="15" t="n"/>
-      <c r="H62" s="15" t="n"/>
+      <c r="A62" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2. Click '+ New' &gt; 'File upload' &gt; Select one or more .xlsx files</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="B63" s="16" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C63" s="16" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="D63" s="16" t="inlineStr">
-        <is>
-          <t>Complete organizational document suite</t>
-        </is>
-      </c>
-      <c r="E63" s="16" t="n"/>
-      <c r="F63" s="16" t="n"/>
-      <c r="G63" s="16" t="n"/>
-      <c r="H63" s="16" t="n"/>
-    </row>
-    <row r="64" ht="20" customHeight="1"/>
-    <row r="65" ht="20" customHeight="1"/>
+      <c r="A63" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3. Double-click the uploaded file to open in Google Sheets</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4. Google Sheets will automatically convert the file</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5. Click 'File' &gt; 'Save as Google Sheets' for native version</t>
+        </is>
+      </c>
+    </row>
     <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  GOOGLE SHEETS SETUP INSTRUCTIONS</t>
+      <c r="A66" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6. Share via 'Share' button with team members</t>
         </is>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1. Open Google Drive (drive.google.com)</t>
+          <t xml:space="preserve">  7. Set permissions: 'Editor' for relevant team, 'Viewer' for others</t>
         </is>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2. Click '+ New' &gt; 'File upload' &gt; Select one or more .xlsx files</t>
+          <t xml:space="preserve">  8. Copy the URL and paste in the 'Google Sheets Link' column above</t>
         </is>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3. Double-click the uploaded file to open in Google Sheets</t>
+          <t xml:space="preserve">  </t>
         </is>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4. Google Sheets will automatically convert the file</t>
+          <t xml:space="preserve">  TIP: All dropdown validations, colors, and formatting are preserved!</t>
         </is>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5. Click 'File' &gt; 'Save as Google Sheets' for native version</t>
+          <t xml:space="preserve">  TIP: Use 'File &gt; Make a copy' to create new templates from filled ones.</t>
         </is>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  6. Share via 'Share' button with team members</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  7. Set permissions: 'Editor' for relevant team, 'Viewer' for others</t>
+          <t xml:space="preserve">  TIP: Upload all files to a shared 'PECH Documents' folder in Google Drive.</t>
         </is>
       </c>
     </row>
     <row r="74" ht="3" customHeight="1">
-      <c r="A74" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  8. Copy the URL and paste in the 'Google Sheets Link' column above</t>
-        </is>
-      </c>
+      <c r="A74" s="5" t="n"/>
+      <c r="B74" s="5" t="n"/>
+      <c r="C74" s="5" t="n"/>
+      <c r="D74" s="5" t="n"/>
+      <c r="E74" s="5" t="n"/>
+      <c r="F74" s="5" t="n"/>
+      <c r="G74" s="5" t="n"/>
+      <c r="H74" s="5" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  </t>
-        </is>
-      </c>
+      <c r="A75" s="18" t="inlineStr">
+        <is>
+          <t>PECH Group Holdings Ltd  |  Confidential  |  pechgroupholdings.tech  |  Technology &amp; Infrastructure Enablers for People</t>
+        </is>
+      </c>
+      <c r="B75" s="19" t="n"/>
+      <c r="C75" s="19" t="n"/>
+      <c r="D75" s="19" t="n"/>
+      <c r="E75" s="19" t="n"/>
+      <c r="F75" s="19" t="n"/>
+      <c r="G75" s="19" t="n"/>
+      <c r="H75" s="19" t="n"/>
     </row>
     <row r="76" ht="3" customHeight="1">
-      <c r="A76" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  TIP: All dropdown validations, colors, and formatting are preserved!</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  TIP: Use 'File &gt; Make a copy' to create new templates from filled ones.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  TIP: Upload all files to a shared 'PECH Documents' folder in Google Drive.</t>
-        </is>
-      </c>
-    </row>
-    <row r="79"/>
-    <row r="80">
-      <c r="A80" s="5" t="n"/>
-      <c r="B80" s="5" t="n"/>
-      <c r="C80" s="5" t="n"/>
-      <c r="D80" s="5" t="n"/>
-      <c r="E80" s="5" t="n"/>
-      <c r="F80" s="5" t="n"/>
-      <c r="G80" s="5" t="n"/>
-      <c r="H80" s="5" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="18" t="inlineStr">
-        <is>
-          <t>PECH Group Holdings Ltd  |  Confidential  |  pechgroupholdings.tech  |  Technology &amp; Infrastructure Enablers for People</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="1" t="n"/>
-      <c r="B82" s="1" t="n"/>
-      <c r="C82" s="1" t="n"/>
-      <c r="D82" s="1" t="n"/>
-      <c r="E82" s="1" t="n"/>
-      <c r="F82" s="1" t="n"/>
-      <c r="G82" s="1" t="n"/>
-      <c r="H82" s="1" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="23" t="inlineStr">
-        <is>
-          <t>PECH GROUP HOLDINGS LTD</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="23" t="inlineStr">
-        <is>
-          <t>PECH GROUP HOLDINGS LTD</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="23" t="inlineStr">
-        <is>
-          <t>PECH GROUP HOLDINGS LTD</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="24" t="inlineStr">
-        <is>
-          <t>Confidential — PECH Group Holdings Ltd — Lagos, Nigeria — pechgroupholdings.tech</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="1" t="n"/>
-      <c r="B88" s="1" t="n"/>
-      <c r="C88" s="1" t="n"/>
-      <c r="D88" s="1" t="n"/>
-      <c r="E88" s="1" t="n"/>
-      <c r="F88" s="1" t="n"/>
-      <c r="G88" s="1" t="n"/>
-      <c r="H88" s="1" t="n"/>
+      <c r="A76" s="1" t="n"/>
+      <c r="B76" s="1" t="n"/>
+      <c r="C76" s="1" t="n"/>
+      <c r="D76" s="1" t="n"/>
+      <c r="E76" s="1" t="n"/>
+      <c r="F76" s="1" t="n"/>
+      <c r="G76" s="1" t="n"/>
+      <c r="H76" s="1" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="19">
     <mergeCell ref="A67:H67"/>
     <mergeCell ref="A64:H64"/>
     <mergeCell ref="A60:H60"/>
     <mergeCell ref="A49:H49"/>
-    <mergeCell ref="A1:H1"/>
     <mergeCell ref="A61:H61"/>
     <mergeCell ref="A70:H70"/>
     <mergeCell ref="A69:H69"/>
-    <mergeCell ref="A87:H87"/>
     <mergeCell ref="A65:H65"/>
     <mergeCell ref="A66:H66"/>
     <mergeCell ref="A75:H75"/>
-    <mergeCell ref="A84:H84"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A86:H86"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A71:H71"/>
-    <mergeCell ref="A85:H85"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="A8:H8"/>
     <mergeCell ref="A62:H62"/>
@@ -2063,15 +1949,6 @@
     <mergeCell ref="A68:H68"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader>&amp;C&amp;8 PECH Group Holdings Ltd | Confidential</oddHeader>
-    <oddFooter>&amp;C&amp;7 PECH Group Holdings Ltd | Lagos, Nigeria | pechgroupholdings.tech</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/employment_xlsx/PECH_MASTER_DOCUMENT_DASHBOARD.xlsx
+++ b/employment_xlsx/PECH_MASTER_DOCUMENT_DASHBOARD.xlsx
@@ -99,14 +99,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000099CC"/>
-        <bgColor rgb="000099CC"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="000099CC"/>
+        <bgColor rgb="000099CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -122,13 +122,19 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
     </border>
     <border>
       <left style="thin">
@@ -150,47 +156,47 @@
   </cellStyleXfs>
   <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -641,1252 +647,1261 @@
       <c r="G6" s="1" t="n"/>
       <c r="H6" s="1" t="n"/>
     </row>
-    <row r="7" ht="8" customHeight="1"/>
+    <row r="7" ht="8" customHeight="1">
+      <c r="A7" s="7" t="n"/>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="n"/>
+      <c r="H7" s="7" t="n"/>
+    </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">  COMPLETE DOCUMENT INDEX (38 Excel Files)</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
-      <c r="E8" s="8" t="n"/>
-      <c r="F8" s="8" t="n"/>
-      <c r="G8" s="8" t="n"/>
-      <c r="H8" s="8" t="n"/>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
+      <c r="G8" s="9" t="n"/>
+      <c r="H8" s="9" t="n"/>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>Document Name</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>Total Records</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="H9" s="9" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>Google Sheets Link</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="n">
+      <c r="A10" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>Full-Time Employment Contract</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>Employment</t>
         </is>
       </c>
-      <c r="D10" s="10" t="n"/>
-      <c r="E10" s="10" t="n"/>
-      <c r="F10" s="10" t="n"/>
-      <c r="G10" s="10" t="n"/>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="D10" s="11" t="n"/>
+      <c r="E10" s="11" t="n"/>
+      <c r="F10" s="11" t="n"/>
+      <c r="G10" s="11" t="n"/>
+      <c r="H10" s="12" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="n">
+      <c r="A11" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>Contract Worker Agreement</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>Employment</t>
         </is>
       </c>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="12" t="n"/>
-      <c r="G11" s="12" t="n"/>
-      <c r="H11" s="13" t="inlineStr">
+      <c r="D11" s="13" t="n"/>
+      <c r="E11" s="13" t="n"/>
+      <c r="F11" s="13" t="n"/>
+      <c r="G11" s="13" t="n"/>
+      <c r="H11" s="14" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="n">
+      <c r="A12" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>Internship Agreement</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>Employment</t>
         </is>
       </c>
-      <c r="D12" s="10" t="n"/>
-      <c r="E12" s="10" t="n"/>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="10" t="n"/>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="D12" s="11" t="n"/>
+      <c r="E12" s="11" t="n"/>
+      <c r="F12" s="11" t="n"/>
+      <c r="G12" s="11" t="n"/>
+      <c r="H12" s="12" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="n">
+      <c r="A13" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>Office Marketer Agreement</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>Employment</t>
         </is>
       </c>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="12" t="n"/>
-      <c r="F13" s="12" t="n"/>
-      <c r="G13" s="12" t="n"/>
-      <c r="H13" s="13" t="inlineStr">
+      <c r="D13" s="13" t="n"/>
+      <c r="E13" s="13" t="n"/>
+      <c r="F13" s="13" t="n"/>
+      <c r="G13" s="13" t="n"/>
+      <c r="H13" s="14" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="n">
+      <c r="A14" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>Commission Marketer Agreement</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>Employment</t>
         </is>
       </c>
-      <c r="D14" s="10" t="n"/>
-      <c r="E14" s="10" t="n"/>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="10" t="n"/>
-      <c r="H14" s="11" t="inlineStr">
+      <c r="D14" s="11" t="n"/>
+      <c r="E14" s="11" t="n"/>
+      <c r="F14" s="11" t="n"/>
+      <c r="G14" s="11" t="n"/>
+      <c r="H14" s="12" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="n">
+      <c r="A15" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>Installer Agreement</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>Employment</t>
         </is>
       </c>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="12" t="n"/>
-      <c r="F15" s="12" t="n"/>
-      <c r="G15" s="12" t="n"/>
-      <c r="H15" s="13" t="inlineStr">
+      <c r="D15" s="13" t="n"/>
+      <c r="E15" s="13" t="n"/>
+      <c r="F15" s="13" t="n"/>
+      <c r="G15" s="13" t="n"/>
+      <c r="H15" s="14" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="n">
+      <c r="A16" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>API Developer Agreement</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>Employment</t>
         </is>
       </c>
-      <c r="D16" s="10" t="n"/>
-      <c r="E16" s="10" t="n"/>
-      <c r="F16" s="10" t="n"/>
-      <c r="G16" s="10" t="n"/>
-      <c r="H16" s="11" t="inlineStr">
+      <c r="D16" s="11" t="n"/>
+      <c r="E16" s="11" t="n"/>
+      <c r="F16" s="11" t="n"/>
+      <c r="G16" s="11" t="n"/>
+      <c r="H16" s="12" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="n">
+      <c r="A17" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>Guarantor / Surety Form</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr">
+      <c r="C17" s="13" t="inlineStr">
         <is>
           <t>Employment</t>
         </is>
       </c>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="12" t="n"/>
-      <c r="F17" s="12" t="n"/>
-      <c r="G17" s="12" t="n"/>
-      <c r="H17" s="13" t="inlineStr">
+      <c r="D17" s="13" t="n"/>
+      <c r="E17" s="13" t="n"/>
+      <c r="F17" s="13" t="n"/>
+      <c r="G17" s="13" t="n"/>
+      <c r="H17" s="14" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="n">
+      <c r="A18" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>Non-Disclosure Agreement</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>Employment</t>
         </is>
       </c>
-      <c r="D18" s="10" t="n"/>
-      <c r="E18" s="10" t="n"/>
-      <c r="F18" s="10" t="n"/>
-      <c r="G18" s="10" t="n"/>
-      <c r="H18" s="11" t="inlineStr">
+      <c r="D18" s="11" t="n"/>
+      <c r="E18" s="11" t="n"/>
+      <c r="F18" s="11" t="n"/>
+      <c r="G18" s="11" t="n"/>
+      <c r="H18" s="12" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="n">
+      <c r="A19" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>Candidate Application Form</t>
         </is>
       </c>
-      <c r="C19" s="12" t="inlineStr">
+      <c r="C19" s="13" t="inlineStr">
         <is>
           <t>HR Form</t>
         </is>
       </c>
-      <c r="D19" s="12" t="n"/>
-      <c r="E19" s="12" t="n"/>
-      <c r="F19" s="12" t="n"/>
-      <c r="G19" s="12" t="n"/>
-      <c r="H19" s="13" t="inlineStr">
+      <c r="D19" s="13" t="n"/>
+      <c r="E19" s="13" t="n"/>
+      <c r="F19" s="13" t="n"/>
+      <c r="G19" s="13" t="n"/>
+      <c r="H19" s="14" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="n">
+      <c r="A20" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>Interview Process &amp; Checklist</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>HR Form</t>
         </is>
       </c>
-      <c r="D20" s="10" t="n"/>
-      <c r="E20" s="10" t="n"/>
-      <c r="F20" s="10" t="n"/>
-      <c r="G20" s="10" t="n"/>
-      <c r="H20" s="11" t="inlineStr">
+      <c r="D20" s="11" t="n"/>
+      <c r="E20" s="11" t="n"/>
+      <c r="F20" s="11" t="n"/>
+      <c r="G20" s="11" t="n"/>
+      <c r="H20" s="12" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="n">
+      <c r="A21" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B21" s="13" t="inlineStr">
         <is>
           <t>Leave Request Form</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr">
+      <c r="C21" s="13" t="inlineStr">
         <is>
           <t>HR Form</t>
         </is>
       </c>
-      <c r="D21" s="12" t="n"/>
-      <c r="E21" s="12" t="n"/>
-      <c r="F21" s="12" t="n"/>
-      <c r="G21" s="12" t="n"/>
-      <c r="H21" s="13" t="inlineStr">
+      <c r="D21" s="13" t="n"/>
+      <c r="E21" s="13" t="n"/>
+      <c r="F21" s="13" t="n"/>
+      <c r="G21" s="13" t="n"/>
+      <c r="H21" s="14" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="n">
+      <c r="A22" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>Staff ID Card Request</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>HR Form</t>
         </is>
       </c>
-      <c r="D22" s="10" t="n"/>
-      <c r="E22" s="10" t="n"/>
-      <c r="F22" s="10" t="n"/>
-      <c r="G22" s="10" t="n"/>
-      <c r="H22" s="11" t="inlineStr">
+      <c r="D22" s="11" t="n"/>
+      <c r="E22" s="11" t="n"/>
+      <c r="F22" s="11" t="n"/>
+      <c r="G22" s="11" t="n"/>
+      <c r="H22" s="12" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="n">
+      <c r="A23" s="13" t="n">
         <v>14</v>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B23" s="13" t="inlineStr">
         <is>
           <t>Job Requirements Handbook</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr">
+      <c r="C23" s="13" t="inlineStr">
         <is>
           <t>HR Reference</t>
         </is>
       </c>
-      <c r="D23" s="12" t="n"/>
-      <c r="E23" s="12" t="n"/>
-      <c r="F23" s="12" t="n"/>
-      <c r="G23" s="12" t="n"/>
-      <c r="H23" s="13" t="inlineStr">
+      <c r="D23" s="13" t="n"/>
+      <c r="E23" s="13" t="n"/>
+      <c r="F23" s="13" t="n"/>
+      <c r="G23" s="13" t="n"/>
+      <c r="H23" s="14" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL)</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="n">
+      <c r="A24" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>Schedule B: KPI Templates</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
         <is>
           <t>HR Reference</t>
         </is>
       </c>
-      <c r="D24" s="10" t="n"/>
-      <c r="E24" s="10" t="n"/>
-      <c r="F24" s="10" t="n"/>
-      <c r="G24" s="10" t="n"/>
-      <c r="H24" s="11" t="inlineStr">
+      <c r="D24" s="11" t="n"/>
+      <c r="E24" s="11" t="n"/>
+      <c r="F24" s="11" t="n"/>
+      <c r="G24" s="11" t="n"/>
+      <c r="H24" s="12" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="n">
+      <c r="A25" s="13" t="n">
         <v>16</v>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B25" s="13" t="inlineStr">
         <is>
           <t>Sales Invoice (Tax Invoice)</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="C25" s="13" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="D25" s="12" t="n"/>
-      <c r="E25" s="12" t="n"/>
-      <c r="F25" s="12" t="n"/>
-      <c r="G25" s="12" t="n"/>
-      <c r="H25" s="13" t="inlineStr">
+      <c r="D25" s="13" t="n"/>
+      <c r="E25" s="13" t="n"/>
+      <c r="F25" s="13" t="n"/>
+      <c r="G25" s="13" t="n"/>
+      <c r="H25" s="14" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="n">
+      <c r="A26" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>Proforma Invoice</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C26" s="11" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="D26" s="10" t="n"/>
-      <c r="E26" s="10" t="n"/>
-      <c r="F26" s="10" t="n"/>
-      <c r="G26" s="10" t="n"/>
-      <c r="H26" s="11" t="inlineStr">
+      <c r="D26" s="11" t="n"/>
+      <c r="E26" s="11" t="n"/>
+      <c r="F26" s="11" t="n"/>
+      <c r="G26" s="11" t="n"/>
+      <c r="H26" s="12" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="n">
+      <c r="A27" s="13" t="n">
         <v>18</v>
       </c>
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B27" s="13" t="inlineStr">
         <is>
           <t>Quotation</t>
         </is>
       </c>
-      <c r="C27" s="12" t="inlineStr">
+      <c r="C27" s="13" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="D27" s="12" t="n"/>
-      <c r="E27" s="12" t="n"/>
-      <c r="F27" s="12" t="n"/>
-      <c r="G27" s="12" t="n"/>
-      <c r="H27" s="13" t="inlineStr">
+      <c r="D27" s="13" t="n"/>
+      <c r="E27" s="13" t="n"/>
+      <c r="F27" s="13" t="n"/>
+      <c r="G27" s="13" t="n"/>
+      <c r="H27" s="14" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL)</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="n">
+      <c r="A28" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="B28" s="10" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>Purchase Order</t>
         </is>
       </c>
-      <c r="C28" s="10" t="inlineStr">
+      <c r="C28" s="11" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="D28" s="10" t="n"/>
-      <c r="E28" s="10" t="n"/>
-      <c r="F28" s="10" t="n"/>
-      <c r="G28" s="10" t="n"/>
-      <c r="H28" s="11" t="inlineStr">
+      <c r="D28" s="11" t="n"/>
+      <c r="E28" s="11" t="n"/>
+      <c r="F28" s="11" t="n"/>
+      <c r="G28" s="11" t="n"/>
+      <c r="H28" s="12" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="n">
+      <c r="A29" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="B29" s="12" t="inlineStr">
+      <c r="B29" s="13" t="inlineStr">
         <is>
           <t>Credit Note</t>
         </is>
       </c>
-      <c r="C29" s="12" t="inlineStr">
+      <c r="C29" s="13" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="D29" s="12" t="n"/>
-      <c r="E29" s="12" t="n"/>
-      <c r="F29" s="12" t="n"/>
-      <c r="G29" s="12" t="n"/>
-      <c r="H29" s="13" t="inlineStr">
+      <c r="D29" s="13" t="n"/>
+      <c r="E29" s="13" t="n"/>
+      <c r="F29" s="13" t="n"/>
+      <c r="G29" s="13" t="n"/>
+      <c r="H29" s="14" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="n">
+      <c r="A30" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="B30" s="10" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>Debit Note</t>
         </is>
       </c>
-      <c r="C30" s="10" t="inlineStr">
+      <c r="C30" s="11" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="D30" s="10" t="n"/>
-      <c r="E30" s="10" t="n"/>
-      <c r="F30" s="10" t="n"/>
-      <c r="G30" s="10" t="n"/>
-      <c r="H30" s="11" t="inlineStr">
+      <c r="D30" s="11" t="n"/>
+      <c r="E30" s="11" t="n"/>
+      <c r="F30" s="11" t="n"/>
+      <c r="G30" s="11" t="n"/>
+      <c r="H30" s="12" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="n">
+      <c r="A31" s="13" t="n">
         <v>22</v>
       </c>
-      <c r="B31" s="12" t="inlineStr">
+      <c r="B31" s="13" t="inlineStr">
         <is>
           <t>Payment Voucher</t>
         </is>
       </c>
-      <c r="C31" s="12" t="inlineStr">
+      <c r="C31" s="13" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="D31" s="12" t="n"/>
-      <c r="E31" s="12" t="n"/>
-      <c r="F31" s="12" t="n"/>
-      <c r="G31" s="12" t="n"/>
-      <c r="H31" s="13" t="inlineStr">
+      <c r="D31" s="13" t="n"/>
+      <c r="E31" s="13" t="n"/>
+      <c r="F31" s="13" t="n"/>
+      <c r="G31" s="13" t="n"/>
+      <c r="H31" s="14" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="n">
+      <c r="A32" s="11" t="n">
         <v>23</v>
       </c>
-      <c r="B32" s="10" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>Payment Receipt</t>
         </is>
       </c>
-      <c r="C32" s="10" t="inlineStr">
+      <c r="C32" s="11" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="D32" s="10" t="n"/>
-      <c r="E32" s="10" t="n"/>
-      <c r="F32" s="10" t="n"/>
-      <c r="G32" s="10" t="n"/>
-      <c r="H32" s="11" t="inlineStr">
+      <c r="D32" s="11" t="n"/>
+      <c r="E32" s="11" t="n"/>
+      <c r="F32" s="11" t="n"/>
+      <c r="G32" s="11" t="n"/>
+      <c r="H32" s="12" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="12" t="n">
+      <c r="A33" s="13" t="n">
         <v>24</v>
       </c>
-      <c r="B33" s="12" t="inlineStr">
+      <c r="B33" s="13" t="inlineStr">
         <is>
           <t>Expense Report</t>
         </is>
       </c>
-      <c r="C33" s="12" t="inlineStr">
+      <c r="C33" s="13" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="D33" s="12" t="n"/>
-      <c r="E33" s="12" t="n"/>
-      <c r="F33" s="12" t="n"/>
-      <c r="G33" s="12" t="n"/>
-      <c r="H33" s="13" t="inlineStr">
+      <c r="D33" s="13" t="n"/>
+      <c r="E33" s="13" t="n"/>
+      <c r="F33" s="13" t="n"/>
+      <c r="G33" s="13" t="n"/>
+      <c r="H33" s="14" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL)</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="n">
+      <c r="A34" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="B34" s="10" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr">
         <is>
           <t>Petty Cash Voucher</t>
         </is>
       </c>
-      <c r="C34" s="10" t="inlineStr">
+      <c r="C34" s="11" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="D34" s="10" t="n"/>
-      <c r="E34" s="10" t="n"/>
-      <c r="F34" s="10" t="n"/>
-      <c r="G34" s="10" t="n"/>
-      <c r="H34" s="11" t="inlineStr">
+      <c r="D34" s="11" t="n"/>
+      <c r="E34" s="11" t="n"/>
+      <c r="F34" s="11" t="n"/>
+      <c r="G34" s="11" t="n"/>
+      <c r="H34" s="12" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL)</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="12" t="n">
+      <c r="A35" s="13" t="n">
         <v>26</v>
       </c>
-      <c r="B35" s="12" t="inlineStr">
+      <c r="B35" s="13" t="inlineStr">
         <is>
           <t>Delivery Note</t>
         </is>
       </c>
-      <c r="C35" s="12" t="inlineStr">
+      <c r="C35" s="13" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="D35" s="12" t="n"/>
-      <c r="E35" s="12" t="n"/>
-      <c r="F35" s="12" t="n"/>
-      <c r="G35" s="12" t="n"/>
-      <c r="H35" s="13" t="inlineStr">
+      <c r="D35" s="13" t="n"/>
+      <c r="E35" s="13" t="n"/>
+      <c r="F35" s="13" t="n"/>
+      <c r="G35" s="13" t="n"/>
+      <c r="H35" s="14" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL)</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="n">
+      <c r="A36" s="11" t="n">
         <v>27</v>
       </c>
-      <c r="B36" s="10" t="inlineStr">
+      <c r="B36" s="11" t="inlineStr">
         <is>
           <t>Goods Received Note</t>
         </is>
       </c>
-      <c r="C36" s="10" t="inlineStr">
+      <c r="C36" s="11" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="D36" s="10" t="n"/>
-      <c r="E36" s="10" t="n"/>
-      <c r="F36" s="10" t="n"/>
-      <c r="G36" s="10" t="n"/>
-      <c r="H36" s="11" t="inlineStr">
+      <c r="D36" s="11" t="n"/>
+      <c r="E36" s="11" t="n"/>
+      <c r="F36" s="11" t="n"/>
+      <c r="G36" s="11" t="n"/>
+      <c r="H36" s="12" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL)</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="12" t="n">
+      <c r="A37" s="13" t="n">
         <v>28</v>
       </c>
-      <c r="B37" s="12" t="inlineStr">
+      <c r="B37" s="13" t="inlineStr">
         <is>
           <t>Stock Requisition Form</t>
         </is>
       </c>
-      <c r="C37" s="12" t="inlineStr">
+      <c r="C37" s="13" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="D37" s="12" t="n"/>
-      <c r="E37" s="12" t="n"/>
-      <c r="F37" s="12" t="n"/>
-      <c r="G37" s="12" t="n"/>
-      <c r="H37" s="13" t="inlineStr">
+      <c r="D37" s="13" t="n"/>
+      <c r="E37" s="13" t="n"/>
+      <c r="F37" s="13" t="n"/>
+      <c r="G37" s="13" t="n"/>
+      <c r="H37" s="14" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL)</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="n">
+      <c r="A38" s="11" t="n">
         <v>29</v>
       </c>
-      <c r="B38" s="10" t="inlineStr">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>Waybill</t>
         </is>
       </c>
-      <c r="C38" s="10" t="inlineStr">
+      <c r="C38" s="11" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="D38" s="10" t="n"/>
-      <c r="E38" s="10" t="n"/>
-      <c r="F38" s="10" t="n"/>
-      <c r="G38" s="10" t="n"/>
-      <c r="H38" s="11" t="inlineStr">
+      <c r="D38" s="11" t="n"/>
+      <c r="E38" s="11" t="n"/>
+      <c r="F38" s="11" t="n"/>
+      <c r="G38" s="11" t="n"/>
+      <c r="H38" s="12" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL)</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="12" t="n">
+      <c r="A39" s="13" t="n">
         <v>30</v>
       </c>
-      <c r="B39" s="12" t="inlineStr">
+      <c r="B39" s="13" t="inlineStr">
         <is>
           <t>Work Order</t>
         </is>
       </c>
-      <c r="C39" s="12" t="inlineStr">
+      <c r="C39" s="13" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="D39" s="12" t="n"/>
-      <c r="E39" s="12" t="n"/>
-      <c r="F39" s="12" t="n"/>
-      <c r="G39" s="12" t="n"/>
-      <c r="H39" s="13" t="inlineStr">
+      <c r="D39" s="13" t="n"/>
+      <c r="E39" s="13" t="n"/>
+      <c r="F39" s="13" t="n"/>
+      <c r="G39" s="13" t="n"/>
+      <c r="H39" s="14" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL)</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="n">
+      <c r="A40" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="B40" s="10" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>Job Completion Report</t>
         </is>
       </c>
-      <c r="C40" s="10" t="inlineStr">
+      <c r="C40" s="11" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="D40" s="10" t="n"/>
-      <c r="E40" s="10" t="n"/>
-      <c r="F40" s="10" t="n"/>
-      <c r="G40" s="10" t="n"/>
-      <c r="H40" s="11" t="inlineStr">
+      <c r="D40" s="11" t="n"/>
+      <c r="E40" s="11" t="n"/>
+      <c r="F40" s="11" t="n"/>
+      <c r="G40" s="11" t="n"/>
+      <c r="H40" s="12" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL)</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="12" t="n">
+      <c r="A41" s="13" t="n">
         <v>32</v>
       </c>
-      <c r="B41" s="12" t="inlineStr">
+      <c r="B41" s="13" t="inlineStr">
         <is>
           <t>Asset Register / Tracking Form</t>
         </is>
       </c>
-      <c r="C41" s="12" t="inlineStr">
+      <c r="C41" s="13" t="inlineStr">
         <is>
           <t>Assets</t>
         </is>
       </c>
-      <c r="D41" s="12" t="n"/>
-      <c r="E41" s="12" t="n"/>
-      <c r="F41" s="12" t="n"/>
-      <c r="G41" s="12" t="n"/>
-      <c r="H41" s="13" t="inlineStr">
+      <c r="D41" s="13" t="n"/>
+      <c r="E41" s="13" t="n"/>
+      <c r="F41" s="13" t="n"/>
+      <c r="G41" s="13" t="n"/>
+      <c r="H41" s="14" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL)</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="10" t="n">
+      <c r="A42" s="11" t="n">
         <v>33</v>
       </c>
-      <c r="B42" s="10" t="inlineStr">
+      <c r="B42" s="11" t="inlineStr">
         <is>
           <t>Visitor Log</t>
         </is>
       </c>
-      <c r="C42" s="10" t="inlineStr">
+      <c r="C42" s="11" t="inlineStr">
         <is>
           <t>Facilities</t>
         </is>
       </c>
-      <c r="D42" s="10" t="n"/>
-      <c r="E42" s="10" t="n"/>
-      <c r="F42" s="10" t="n"/>
-      <c r="G42" s="10" t="n"/>
-      <c r="H42" s="11" t="inlineStr">
+      <c r="D42" s="11" t="n"/>
+      <c r="E42" s="11" t="n"/>
+      <c r="F42" s="11" t="n"/>
+      <c r="G42" s="11" t="n"/>
+      <c r="H42" s="12" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL)</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="12" t="n">
+      <c r="A43" s="13" t="n">
         <v>34</v>
       </c>
-      <c r="B43" s="12" t="inlineStr">
+      <c r="B43" s="13" t="inlineStr">
         <is>
           <t>Incident Report Form</t>
         </is>
       </c>
-      <c r="C43" s="12" t="inlineStr">
+      <c r="C43" s="13" t="inlineStr">
         <is>
           <t>Safety</t>
         </is>
       </c>
-      <c r="D43" s="12" t="n"/>
-      <c r="E43" s="12" t="n"/>
-      <c r="F43" s="12" t="n"/>
-      <c r="G43" s="12" t="n"/>
-      <c r="H43" s="13" t="inlineStr">
+      <c r="D43" s="13" t="n"/>
+      <c r="E43" s="13" t="n"/>
+      <c r="F43" s="13" t="n"/>
+      <c r="G43" s="13" t="n"/>
+      <c r="H43" s="14" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL)</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="n">
+      <c r="A44" s="11" t="n">
         <v>35</v>
       </c>
-      <c r="B44" s="10" t="inlineStr">
+      <c r="B44" s="11" t="inlineStr">
         <is>
           <t>Media &amp; Public Communications</t>
         </is>
       </c>
-      <c r="C44" s="10" t="inlineStr">
+      <c r="C44" s="11" t="inlineStr">
         <is>
           <t>Policy</t>
         </is>
       </c>
-      <c r="D44" s="10" t="n"/>
-      <c r="E44" s="10" t="n"/>
-      <c r="F44" s="10" t="n"/>
-      <c r="G44" s="10" t="n"/>
-      <c r="H44" s="11" t="inlineStr">
+      <c r="D44" s="11" t="n"/>
+      <c r="E44" s="11" t="n"/>
+      <c r="F44" s="11" t="n"/>
+      <c r="G44" s="11" t="n"/>
+      <c r="H44" s="12" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL)</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="12" t="n">
+      <c r="A45" s="13" t="n">
         <v>36</v>
       </c>
-      <c r="B45" s="12" t="inlineStr">
+      <c r="B45" s="13" t="inlineStr">
         <is>
           <t>Hackathon Rules &amp; Guidelines</t>
         </is>
       </c>
-      <c r="C45" s="12" t="inlineStr">
+      <c r="C45" s="13" t="inlineStr">
         <is>
           <t>Events</t>
         </is>
       </c>
-      <c r="D45" s="12" t="n"/>
-      <c r="E45" s="12" t="n"/>
-      <c r="F45" s="12" t="n"/>
-      <c r="G45" s="12" t="n"/>
-      <c r="H45" s="13" t="inlineStr">
+      <c r="D45" s="13" t="n"/>
+      <c r="E45" s="13" t="n"/>
+      <c r="F45" s="13" t="n"/>
+      <c r="G45" s="13" t="n"/>
+      <c r="H45" s="14" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL)</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="10" t="n">
+      <c r="A46" s="11" t="n">
         <v>37</v>
       </c>
-      <c r="B46" s="10" t="inlineStr">
+      <c r="B46" s="11" t="inlineStr">
         <is>
           <t>Installation Completion Certificate</t>
         </is>
       </c>
-      <c r="C46" s="10" t="inlineStr">
+      <c r="C46" s="11" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="D46" s="10" t="n"/>
-      <c r="E46" s="10" t="n"/>
-      <c r="F46" s="10" t="n"/>
-      <c r="G46" s="10" t="n"/>
-      <c r="H46" s="11" t="inlineStr">
+      <c r="D46" s="11" t="n"/>
+      <c r="E46" s="11" t="n"/>
+      <c r="F46" s="11" t="n"/>
+      <c r="G46" s="11" t="n"/>
+      <c r="H46" s="12" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL)</t>
         </is>
       </c>
     </row>
     <row r="49" ht="26" customHeight="1">
-      <c r="A49" s="7" t="inlineStr">
+      <c r="A49" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">  DOCUMENT CATEGORIES SUMMARY</t>
         </is>
       </c>
-      <c r="B49" s="8" t="n"/>
-      <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="n"/>
-      <c r="E49" s="8" t="n"/>
-      <c r="F49" s="8" t="n"/>
-      <c r="G49" s="8" t="n"/>
-      <c r="H49" s="8" t="n"/>
+      <c r="B49" s="9" t="n"/>
+      <c r="C49" s="9" t="n"/>
+      <c r="D49" s="9" t="n"/>
+      <c r="E49" s="9" t="n"/>
+      <c r="F49" s="9" t="n"/>
+      <c r="G49" s="9" t="n"/>
+      <c r="H49" s="9" t="n"/>
     </row>
     <row r="50" ht="28" customHeight="1">
-      <c r="A50" s="9" t="inlineStr">
+      <c r="A50" s="10" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B50" s="9" t="inlineStr">
+      <c r="B50" s="10" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C50" s="9" t="inlineStr">
+      <c r="C50" s="10" t="inlineStr">
         <is>
           <t>Document Count</t>
         </is>
       </c>
-      <c r="D50" s="9" t="inlineStr">
+      <c r="D50" s="10" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E50" s="9" t="inlineStr"/>
-      <c r="F50" s="9" t="inlineStr"/>
-      <c r="G50" s="9" t="inlineStr"/>
-      <c r="H50" s="9" t="inlineStr"/>
+      <c r="E50" s="10" t="inlineStr"/>
+      <c r="F50" s="10" t="inlineStr"/>
+      <c r="G50" s="10" t="inlineStr"/>
+      <c r="H50" s="10" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="14" t="n">
+      <c r="A51" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="B51" s="14" t="inlineStr">
+      <c r="B51" s="15" t="inlineStr">
         <is>
           <t>Employment Contracts</t>
         </is>
       </c>
-      <c r="C51" s="14" t="inlineStr">
+      <c r="C51" s="15" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D51" s="14" t="inlineStr">
+      <c r="D51" s="15" t="inlineStr">
         <is>
           <t>All employment and contractor agreements</t>
         </is>
       </c>
-      <c r="E51" s="14" t="n"/>
-      <c r="F51" s="14" t="n"/>
-      <c r="G51" s="14" t="n"/>
-      <c r="H51" s="14" t="n"/>
+      <c r="E51" s="15" t="n"/>
+      <c r="F51" s="15" t="n"/>
+      <c r="G51" s="15" t="n"/>
+      <c r="H51" s="15" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="15" t="n">
+      <c r="A52" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="B52" s="15" t="inlineStr">
+      <c r="B52" s="16" t="inlineStr">
         <is>
           <t>HR Forms</t>
         </is>
       </c>
-      <c r="C52" s="15" t="inlineStr">
+      <c r="C52" s="16" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D52" s="15" t="inlineStr">
+      <c r="D52" s="16" t="inlineStr">
         <is>
           <t>Application, interview, leave, ID, handbook, KPIs</t>
         </is>
       </c>
-      <c r="E52" s="15" t="n"/>
-      <c r="F52" s="15" t="n"/>
-      <c r="G52" s="15" t="n"/>
-      <c r="H52" s="15" t="n"/>
+      <c r="E52" s="16" t="n"/>
+      <c r="F52" s="16" t="n"/>
+      <c r="G52" s="16" t="n"/>
+      <c r="H52" s="16" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="14" t="n">
+      <c r="A53" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="B53" s="14" t="inlineStr">
+      <c r="B53" s="15" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="C53" s="14" t="inlineStr">
+      <c r="C53" s="15" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D53" s="14" t="inlineStr">
+      <c r="D53" s="15" t="inlineStr">
         <is>
           <t>Invoices, POs, quotations, vouchers, receipts, notes</t>
         </is>
       </c>
-      <c r="E53" s="14" t="n"/>
-      <c r="F53" s="14" t="n"/>
-      <c r="G53" s="14" t="n"/>
-      <c r="H53" s="14" t="n"/>
+      <c r="E53" s="15" t="n"/>
+      <c r="F53" s="15" t="n"/>
+      <c r="G53" s="15" t="n"/>
+      <c r="H53" s="15" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="15" t="n">
+      <c r="A54" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="B54" s="15" t="inlineStr">
+      <c r="B54" s="16" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="C54" s="15" t="inlineStr">
+      <c r="C54" s="16" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D54" s="15" t="inlineStr">
+      <c r="D54" s="16" t="inlineStr">
         <is>
           <t>Delivery, GRN, stock, waybill, work orders, jobs</t>
         </is>
       </c>
-      <c r="E54" s="15" t="n"/>
-      <c r="F54" s="15" t="n"/>
-      <c r="G54" s="15" t="n"/>
-      <c r="H54" s="15" t="n"/>
+      <c r="E54" s="16" t="n"/>
+      <c r="F54" s="16" t="n"/>
+      <c r="G54" s="16" t="n"/>
+      <c r="H54" s="16" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="14" t="n">
+      <c r="A55" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="B55" s="14" t="inlineStr">
+      <c r="B55" s="15" t="inlineStr">
         <is>
           <t>Assets / Facilities / Safety</t>
         </is>
       </c>
-      <c r="C55" s="14" t="inlineStr">
+      <c r="C55" s="15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D55" s="14" t="inlineStr">
+      <c r="D55" s="15" t="inlineStr">
         <is>
           <t>Asset register, visitor log, incident reports</t>
         </is>
       </c>
-      <c r="E55" s="14" t="n"/>
-      <c r="F55" s="14" t="n"/>
-      <c r="G55" s="14" t="n"/>
-      <c r="H55" s="14" t="n"/>
+      <c r="E55" s="15" t="n"/>
+      <c r="F55" s="15" t="n"/>
+      <c r="G55" s="15" t="n"/>
+      <c r="H55" s="15" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="15" t="n">
+      <c r="A56" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="B56" s="15" t="inlineStr">
+      <c r="B56" s="16" t="inlineStr">
         <is>
           <t>Policy &amp; Events</t>
         </is>
       </c>
-      <c r="C56" s="15" t="inlineStr">
+      <c r="C56" s="16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D56" s="15" t="inlineStr">
+      <c r="D56" s="16" t="inlineStr">
         <is>
           <t>Media policy, hackathon tracker</t>
         </is>
       </c>
-      <c r="E56" s="15" t="n"/>
-      <c r="F56" s="15" t="n"/>
-      <c r="G56" s="15" t="n"/>
-      <c r="H56" s="15" t="n"/>
+      <c r="E56" s="16" t="n"/>
+      <c r="F56" s="16" t="n"/>
+      <c r="G56" s="16" t="n"/>
+      <c r="H56" s="16" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="16" t="n">
+      <c r="A57" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="B57" s="16" t="inlineStr">
+      <c r="B57" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C57" s="16" t="inlineStr">
+      <c r="C57" s="17" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D57" s="16" t="inlineStr">
+      <c r="D57" s="17" t="inlineStr">
         <is>
           <t>Complete organizational document suite</t>
         </is>
       </c>
-      <c r="E57" s="16" t="n"/>
-      <c r="F57" s="16" t="n"/>
-      <c r="G57" s="16" t="n"/>
-      <c r="H57" s="16" t="n"/>
+      <c r="E57" s="17" t="n"/>
+      <c r="F57" s="17" t="n"/>
+      <c r="G57" s="17" t="n"/>
+      <c r="H57" s="17" t="n"/>
     </row>
     <row r="60" ht="26" customHeight="1">
-      <c r="A60" s="7" t="inlineStr">
+      <c r="A60" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">  GOOGLE SHEETS SETUP INSTRUCTIONS</t>
         </is>
       </c>
-      <c r="B60" s="8" t="n"/>
-      <c r="C60" s="8" t="n"/>
-      <c r="D60" s="8" t="n"/>
-      <c r="E60" s="8" t="n"/>
-      <c r="F60" s="8" t="n"/>
-      <c r="G60" s="8" t="n"/>
-      <c r="H60" s="8" t="n"/>
+      <c r="B60" s="9" t="n"/>
+      <c r="C60" s="9" t="n"/>
+      <c r="D60" s="9" t="n"/>
+      <c r="E60" s="9" t="n"/>
+      <c r="F60" s="9" t="n"/>
+      <c r="G60" s="9" t="n"/>
+      <c r="H60" s="9" t="n"/>
     </row>
     <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="17" t="inlineStr">
+      <c r="A61" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">  1. Open Google Drive (drive.google.com)</t>
         </is>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="17" t="inlineStr">
+      <c r="A62" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">  2. Click '+ New' &gt; 'File upload' &gt; Select one or more .xlsx files</t>
         </is>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="17" t="inlineStr">
+      <c r="A63" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">  3. Double-click the uploaded file to open in Google Sheets</t>
         </is>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="17" t="inlineStr">
+      <c r="A64" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">  4. Google Sheets will automatically convert the file</t>
         </is>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="17" t="inlineStr">
+      <c r="A65" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">  5. Click 'File' &gt; 'Save as Google Sheets' for native version</t>
         </is>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="17" t="inlineStr">
+      <c r="A66" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">  6. Share via 'Share' button with team members</t>
         </is>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="17" t="inlineStr">
+      <c r="A67" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">  7. Set permissions: 'Editor' for relevant team, 'Viewer' for others</t>
         </is>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="17" t="inlineStr">
+      <c r="A68" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">  8. Copy the URL and paste in the 'Google Sheets Link' column above</t>
         </is>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="17" t="inlineStr">
+      <c r="A69" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">  </t>
         </is>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="17" t="inlineStr">
+      <c r="A70" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">  TIP: All dropdown validations, colors, and formatting are preserved!</t>
         </is>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="17" t="inlineStr">
+      <c r="A71" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">  TIP: Use 'File &gt; Make a copy' to create new templates from filled ones.</t>
         </is>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="17" t="inlineStr">
+      <c r="A72" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">  TIP: Upload all files to a shared 'PECH Documents' folder in Google Drive.</t>
         </is>
@@ -1902,19 +1917,19 @@
       <c r="G74" s="5" t="n"/>
       <c r="H74" s="5" t="n"/>
     </row>
-    <row r="75">
-      <c r="A75" s="18" t="inlineStr">
-        <is>
-          <t>PECH Group Holdings Ltd  |  Confidential  |  pechgroupholdings.tech  |  Technology &amp; Infrastructure Enablers for People</t>
-        </is>
-      </c>
-      <c r="B75" s="19" t="n"/>
-      <c r="C75" s="19" t="n"/>
-      <c r="D75" s="19" t="n"/>
-      <c r="E75" s="19" t="n"/>
-      <c r="F75" s="19" t="n"/>
-      <c r="G75" s="19" t="n"/>
-      <c r="H75" s="19" t="n"/>
+    <row r="75" ht="18" customHeight="1">
+      <c r="A75" s="19" t="inlineStr">
+        <is>
+          <t>Confidential  |  pechgroupholdings.tech  |  Technology &amp; Infrastructure Enablers for People</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="n"/>
+      <c r="C75" s="7" t="n"/>
+      <c r="D75" s="7" t="n"/>
+      <c r="E75" s="7" t="n"/>
+      <c r="F75" s="7" t="n"/>
+      <c r="G75" s="7" t="n"/>
+      <c r="H75" s="7" t="n"/>
     </row>
     <row r="76" ht="3" customHeight="1">
       <c r="A76" s="1" t="n"/>
